--- a/public/exports-from-60/29189668.xlsx
+++ b/public/exports-from-60/29189668.xlsx
@@ -59,7 +59,7 @@
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Areal (m²)</t>
+          <t xml:space="preserve">Opvarmet BBR-areal (m²)</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
@@ -7639,7 +7639,7 @@
       </c>
       <c r="K102" t="inlineStr">
         <is>
-          <t xml:space="preserve">200017658</t>
+          <t xml:space="preserve">200017659</t>
         </is>
       </c>
       <c r="L102" t="inlineStr">
@@ -8539,7 +8539,7 @@
       </c>
       <c r="K114" t="inlineStr">
         <is>
-          <t xml:space="preserve">311215030</t>
+          <t xml:space="preserve">311215043</t>
         </is>
       </c>
       <c r="L114" t="inlineStr">
@@ -24664,7 +24664,7 @@
       </c>
       <c r="K329" t="inlineStr">
         <is>
-          <t xml:space="preserve">311393677</t>
+          <t xml:space="preserve">311393687</t>
         </is>
       </c>
       <c r="L329" t="inlineStr">
@@ -27214,7 +27214,7 @@
       </c>
       <c r="K363" t="inlineStr">
         <is>
-          <t xml:space="preserve">311407500</t>
+          <t xml:space="preserve">311407501</t>
         </is>
       </c>
       <c r="L363" t="inlineStr">
@@ -27289,7 +27289,7 @@
       </c>
       <c r="K364" t="inlineStr">
         <is>
-          <t xml:space="preserve">311407500</t>
+          <t xml:space="preserve">311407501</t>
         </is>
       </c>
       <c r="L364" t="inlineStr">
@@ -27364,7 +27364,7 @@
       </c>
       <c r="K365" t="inlineStr">
         <is>
-          <t xml:space="preserve">311407500</t>
+          <t xml:space="preserve">311407501</t>
         </is>
       </c>
       <c r="L365" t="inlineStr">
@@ -27514,7 +27514,7 @@
       </c>
       <c r="K367" t="inlineStr">
         <is>
-          <t xml:space="preserve">311407500</t>
+          <t xml:space="preserve">311407501</t>
         </is>
       </c>
       <c r="L367" t="inlineStr">
@@ -30739,7 +30739,7 @@
       </c>
       <c r="K410" t="inlineStr">
         <is>
-          <t xml:space="preserve">311424644</t>
+          <t xml:space="preserve">311424656</t>
         </is>
       </c>
       <c r="L410" t="inlineStr">
@@ -30814,7 +30814,7 @@
       </c>
       <c r="K411" t="inlineStr">
         <is>
-          <t xml:space="preserve">311424644</t>
+          <t xml:space="preserve">311424656</t>
         </is>
       </c>
       <c r="L411" t="inlineStr">

--- a/public/exports-from-60/29189668.xlsx
+++ b/public/exports-from-60/29189668.xlsx
@@ -8614,7 +8614,7 @@
       </c>
       <c r="K115" t="inlineStr">
         <is>
-          <t xml:space="preserve">311215051</t>
+          <t xml:space="preserve">311215030</t>
         </is>
       </c>
       <c r="L115" t="inlineStr">
@@ -26689,7 +26689,7 @@
       </c>
       <c r="K356" t="inlineStr">
         <is>
-          <t xml:space="preserve">311407501</t>
+          <t xml:space="preserve">311407500</t>
         </is>
       </c>
       <c r="L356" t="inlineStr">
@@ -26764,7 +26764,7 @@
       </c>
       <c r="K357" t="inlineStr">
         <is>
-          <t xml:space="preserve">311407501</t>
+          <t xml:space="preserve">311407500</t>
         </is>
       </c>
       <c r="L357" t="inlineStr">
@@ -26839,7 +26839,7 @@
       </c>
       <c r="K358" t="inlineStr">
         <is>
-          <t xml:space="preserve">311407501</t>
+          <t xml:space="preserve">311407500</t>
         </is>
       </c>
       <c r="L358" t="inlineStr">
@@ -26989,7 +26989,7 @@
       </c>
       <c r="K360" t="inlineStr">
         <is>
-          <t xml:space="preserve">311407501</t>
+          <t xml:space="preserve">311407500</t>
         </is>
       </c>
       <c r="L360" t="inlineStr">
@@ -30214,7 +30214,7 @@
       </c>
       <c r="K403" t="inlineStr">
         <is>
-          <t xml:space="preserve">311424656</t>
+          <t xml:space="preserve">311424644</t>
         </is>
       </c>
       <c r="L403" t="inlineStr">
@@ -30289,7 +30289,7 @@
       </c>
       <c r="K404" t="inlineStr">
         <is>
-          <t xml:space="preserve">311424656</t>
+          <t xml:space="preserve">311424644</t>
         </is>
       </c>
       <c r="L404" t="inlineStr">
@@ -38314,7 +38314,7 @@
       </c>
       <c r="K511" t="inlineStr">
         <is>
-          <t xml:space="preserve">311929274</t>
+          <t xml:space="preserve">311929271</t>
         </is>
       </c>
       <c r="L511" t="inlineStr">
@@ -38389,7 +38389,7 @@
       </c>
       <c r="K512" t="inlineStr">
         <is>
-          <t xml:space="preserve">311929274</t>
+          <t xml:space="preserve">311929271</t>
         </is>
       </c>
       <c r="L512" t="inlineStr">
@@ -38464,7 +38464,7 @@
       </c>
       <c r="K513" t="inlineStr">
         <is>
-          <t xml:space="preserve">311929274</t>
+          <t xml:space="preserve">311929271</t>
         </is>
       </c>
       <c r="L513" t="inlineStr">
@@ -38539,7 +38539,7 @@
       </c>
       <c r="K514" t="inlineStr">
         <is>
-          <t xml:space="preserve">311929274</t>
+          <t xml:space="preserve">311929271</t>
         </is>
       </c>
       <c r="L514" t="inlineStr">
